--- a/src/attributions/attributions_ig_traj_340.xlsx
+++ b/src/attributions/attributions_ig_traj_340.xlsx
@@ -1571,7 +1571,7 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.06963260286419327</v>
+        <v>-0.1139270562611605</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -1580,10 +1580,10 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.004834780091195144</v>
+        <v>0.04051950850189801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2755992834670435</v>
+        <v>0.08272445964888252</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1598,7 +1598,7 @@
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0002663870652981695</v>
+        <v>-0.0007472136224060395</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -1607,25 +1607,25 @@
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01147065145057566</v>
+        <v>0.02307313214763511</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1122130976987839</v>
+        <v>0.02973090256257998</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02912810838749866</v>
+        <v>-0.04683365852305477</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
@@ -1634,10 +1634,10 @@
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1130889656859922</v>
+        <v>0.07135742206048584</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08587725428102909</v>
+        <v>0.07680160852251755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1646,25 +1646,25 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.02976598011329856</v>
+        <v>0.05369942068490987</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06128216366015359</v>
+        <v>-0.0696687365450884</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.04033101459967986</v>
+        <v>0.02393877405739916</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1679,7 +1679,7 @@
         <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.05976040818130542</v>
+        <v>-0.199992944080718</v>
       </c>
       <c r="AM3" t="n">
         <v>-0</v>
@@ -1688,16 +1688,16 @@
         <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1327444865084387</v>
+        <v>-0.1791111569865475</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1829114606722403</v>
+        <v>0.06845751851757927</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
@@ -1706,34 +1706,34 @@
         <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.2093632418556844</v>
+        <v>-0.539138535166814</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1571996159019665</v>
+        <v>0.09863607848239975</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.5468980946064504</v>
+        <v>0.1487880504814595</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.05513268068010761</v>
+        <v>0.05206744623781907</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,52 +1742,52 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.008217873306295162</v>
+        <v>0.03278505605205467</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.07896157668650544</v>
+        <v>0.0104402528395411</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.06521465113057225</v>
+        <v>0.01408498337447727</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.02016084019902625</v>
+        <v>-0.07172555330813188</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.06402918403603067</v>
+        <v>-0.06919280911830371</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.07849068307218515</v>
+        <v>-0.3676192767457727</v>
       </c>
       <c r="BW3" t="n">
         <v>-0</v>
@@ -1796,43 +1796,43 @@
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1122767404129582</v>
+        <v>0.07273483579570342</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2748711421301279</v>
+        <v>0.1702242492143126</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.04388101659976949</v>
+        <v>0.2382171703043595</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.02346144515891952</v>
+        <v>-0.01749725459277391</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.140831096001662</v>
+        <v>-0.1130659350868869</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0007133717129222553</v>
+        <v>0.1344967537316526</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
@@ -1850,43 +1850,43 @@
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1223487743832092</v>
+        <v>-0.02529378855917856</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.006995231402624408</v>
+        <v>-0.0576926994504522</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.03843198745519356</v>
+        <v>0.2389178064149412</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.00842196214846205</v>
+        <v>-0.01945858214034179</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.16653773930279</v>
+        <v>-0.1151930542352321</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
@@ -1895,61 +1895,61 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.04940674516332027</v>
+        <v>0.0004809960883948058</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.04811360917380263</v>
+        <v>0.02996370446514177</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.01929459173523518</v>
+        <v>-0.04042867348304072</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.02587157508770442</v>
+        <v>0.1392191736720425</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.03359954031775652</v>
+        <v>-0.03404913068688464</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01859923536594222</v>
+        <v>-0.03051579969372115</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.006757550931971714</v>
+        <v>-0.122790817090952</v>
       </c>
       <c r="DY3" t="n">
         <v>-0</v>
@@ -1958,10 +1958,10 @@
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.07867275079609939</v>
+        <v>0.02464920357195741</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01615037179311406</v>
+        <v>0.2965959531650553</v>
       </c>
       <c r="EC3" t="n">
         <v>0</v>
@@ -1970,13 +1970,13 @@
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.05716533668574744</v>
+        <v>0.1398527785178327</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
@@ -1985,25 +1985,25 @@
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.02982964140222009</v>
+        <v>0.004498565452255916</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.1272003032362059</v>
+        <v>-0.0521534731997931</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
         <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.05293239810358619</v>
+        <v>0.1306709974332533</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01324959771890875</v>
+        <v>-0.04507616657532437</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.04655719440691017</v>
+        <v>-0.009616560177204022</v>
       </c>
       <c r="EU3" t="n">
         <v>-0</v>
@@ -2024,31 +2024,31 @@
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.031696154591446</v>
+        <v>0.2609028931247204</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.01026787745553993</v>
+        <v>-0.01435849306733859</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.1301064757432272</v>
+        <v>-0.1129409980604909</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
@@ -2057,73 +2057,73 @@
         <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.05467120775723725</v>
+        <v>0.1033309138780511</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.08175214846090161</v>
+        <v>0.1080569295002565</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0.1514718946304586</v>
+        <v>0.02876180162614661</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
         <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1092918968694736</v>
+        <v>0.2530941927786268</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.007556363514892736</v>
+        <v>-0.006405224582972056</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.2088200244152855</v>
+        <v>-0.1347690090344492</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
         <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.002566257899130676</v>
+        <v>0.0926004790260439</v>
       </c>
       <c r="GA3" t="n">
         <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.02917187592124836</v>
+        <v>-0.01175490682468373</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
@@ -2143,28 +2143,28 @@
         <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04641858978789474</v>
+        <v>-0.007880291208280561</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1408878189176642</v>
+        <v>0.033766361176768</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04357483070413624</v>
+        <v>-0.00754344299714584</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -2173,25 +2173,25 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02333059292082897</v>
+        <v>0.005892474971771172</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06440129372309893</v>
+        <v>0.03967894654405284</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01038955989549833</v>
+        <v>0.00198456570479833</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
         <v>-0</v>
@@ -2203,25 +2203,25 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06538966618049551</v>
+        <v>0.0006220903491594437</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08526184993714514</v>
+        <v>0.03423588142184798</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.08822142212181343</v>
+        <v>0.02741976134392218</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD4" t="n">
         <v>-0</v>
@@ -2230,22 +2230,22 @@
         <v>-0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.04420539260593201</v>
+        <v>-0.01836817384986508</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005999043665138852</v>
+        <v>0.02921087768301086</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.009410141057984553</v>
+        <v>0.006107215705312952</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
         <v>-0</v>
@@ -2254,19 +2254,19 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.05996855386701706</v>
+        <v>-0.02436298428843025</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.05174134028785946</v>
+        <v>-0.0238982972136186</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.05098848793189675</v>
+        <v>-0.002320776119796329</v>
       </c>
       <c r="AS4" t="n">
         <v>-0</v>
@@ -2284,43 +2284,43 @@
         <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1382818766577141</v>
+        <v>0.0309451341754328</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.2789525931497093</v>
+        <v>0.1498475515822555</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.04101040567247605</v>
+        <v>-0.007030735337153306</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE4" t="n">
         <v>-0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.08586122994184742</v>
+        <v>-0.04361392840966919</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.000738639274166532</v>
+        <v>-0.03200511812363344</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.02156183538118569</v>
+        <v>-0.0175562066769754</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2335,46 +2335,46 @@
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.06206730984477252</v>
+        <v>0.01059821040288492</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.04477416343179352</v>
+        <v>0.01352833901016721</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.05501745605303242</v>
+        <v>0.01821275787008914</v>
       </c>
       <c r="BT4" t="n">
         <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
         <v>-0</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.100889010321848</v>
+        <v>-0.003597634420873258</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.221004173231771</v>
+        <v>0.05857665102728854</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0.05951777486618923</v>
+        <v>-0.0178140592824879</v>
       </c>
       <c r="CC4" t="n">
         <v>-0</v>
@@ -2383,25 +2383,25 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.03750933786231721</v>
+        <v>0.004943315338292596</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0.07519399719973868</v>
+        <v>-0.02124994830217568</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.05882653416348887</v>
+        <v>0.02597341425249896</v>
       </c>
       <c r="CL4" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO4" t="n">
         <v>0</v>
@@ -2419,79 +2419,79 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.04888673337669158</v>
+        <v>-0.006959403745522982</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.006029997324482957</v>
+        <v>0.02202177775336812</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.01692613187263528</v>
+        <v>0.03465913991669974</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01795400515030205</v>
+        <v>0.004521711669581937</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0.06981349794581695</v>
+        <v>-0.03164311295485413</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.07539752896326694</v>
+        <v>0.01484557519421422</v>
       </c>
       <c r="DD4" t="n">
         <v>-0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04479792423627288</v>
+        <v>-0.007152791416967779</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0.02625894292025481</v>
+        <v>-0.001220128968445254</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0170953212907851</v>
+        <v>0.007655318755949575</v>
       </c>
       <c r="DM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
@@ -2500,43 +2500,43 @@
         <v>-0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01030186307135301</v>
+        <v>0.06605702524223285</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.02116301889637476</v>
+        <v>-0.05606014304025403</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>-0.02194812353405933</v>
+        <v>0.002734125518971037</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.03278569498434222</v>
+        <v>0.02641299208075929</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0032210717255499</v>
+        <v>-0.03310088732511029</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0009225530920037832</v>
+        <v>-0.01172140817425908</v>
       </c>
       <c r="EE4" t="n">
         <v>0</v>
@@ -2554,70 +2554,70 @@
         <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.003589061174035274</v>
+        <v>-0.01889748781920333</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0.04343210329230824</v>
+        <v>-0.008383249746343585</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.03825189683323815</v>
+        <v>0.01801599261394139</v>
       </c>
       <c r="EN4" t="n">
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
         <v>-0</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.04481169890823097</v>
+        <v>-0.0106839890660814</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0.001836623273024648</v>
+        <v>-0.04167863291083652</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.09240301356069404</v>
+        <v>0.001191005223906388</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
         <v>-0</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.03006267560203897</v>
+        <v>-0.0105048783300806</v>
       </c>
       <c r="FC4" t="n">
-        <v>-0.06671520382392598</v>
+        <v>-0.02812487898637963</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.07817197197459945</v>
+        <v>0.02408072358755173</v>
       </c>
       <c r="FF4" t="n">
         <v>0</v>
@@ -2626,58 +2626,58 @@
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
         <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.03251212530166613</v>
+        <v>-0.01725520468591919</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0.09729728886864082</v>
+        <v>0.01656248120239258</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0780168263740767</v>
+        <v>0.0304051602473608</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.08651034570719345</v>
+        <v>-0.07066298535536235</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.07416857860731878</v>
+        <v>-0.1213099947397747</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>9.975027679305501e-05</v>
+        <v>0.008073446770185554</v>
       </c>
       <c r="FX4" t="n">
         <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
         <v>-0</v>
@@ -2686,19 +2686,19 @@
         <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.006709446404208863</v>
+        <v>-0.02997542900264275</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0.05268188296317966</v>
+        <v>-0.01191554839071327</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2706,19 +2706,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
         <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01239109601957289</v>
+        <v>0.01111750677722356</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1138882289343638</v>
+        <v>0.06453391500353388</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02459921704757467</v>
+        <v>0.07424520308619792</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,31 +2727,31 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.00204472191694334</v>
+        <v>-0.001738038109860573</v>
       </c>
       <c r="M5" t="n">
-        <v>0.112887483160703</v>
+        <v>0.04102399764362862</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02727600431244421</v>
+        <v>0.07752141046686228</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2760,31 +2760,31 @@
         <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.04765121361786447</v>
+        <v>-0.03036472842044376</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07355608955954647</v>
+        <v>0.03912913287577435</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01717454822690289</v>
+        <v>-0.03226511200549106</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -2793,67 +2793,67 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.374704598545163e-11</v>
+        <v>4.62743579673025e-11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.03766405155033386</v>
+        <v>-0.05866578308028576</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.004073871855734741</v>
+        <v>0.01652250493604691</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.008371735913487791</v>
+        <v>-0.06090753368155971</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.05787386495258962</v>
+        <v>0.08302064741338955</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02388574892333921</v>
+        <v>0.0004653972673032166</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.1197830945658923</v>
+        <v>-0.1815734028303921</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1247129024463108</v>
+        <v>0.1484015653850847</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1869973518615732</v>
+        <v>-0.02690518767511401</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -2874,13 +2874,13 @@
         <v>-0</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.03862000232463265</v>
+        <v>0.002518641159528924</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.04370652275605362</v>
+        <v>-0.04898343854452208</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.01720249049210011</v>
+        <v>-0.08488862960889088</v>
       </c>
       <c r="BH5" t="n">
         <v>-0</v>
@@ -2889,25 +2889,25 @@
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>-0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.041160060360411</v>
+        <v>0.04481745618469472</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.04088678590019109</v>
+        <v>0.1120436185471795</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.07445952698054717</v>
+        <v>0.1048973963236362</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
@@ -2916,25 +2916,25 @@
         <v>-0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.1154757831508945</v>
+        <v>-0.09960618473289307</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1428825364465248</v>
+        <v>0.0993309177653123</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.1150370176655985</v>
+        <v>0.02929878708846993</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2943,10 +2943,10 @@
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
@@ -2955,46 +2955,46 @@
         <v>0</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.04883536582586571</v>
+        <v>0.07597617194651499</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.06793107122707262</v>
+        <v>0.0138684531645038</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0007018779762435649</v>
+        <v>-0.1014133036731461</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.01547702994343069</v>
+        <v>0.004440007490660648</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.007684998626269031</v>
+        <v>0.06375788847994326</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.04069290824601238</v>
+        <v>0.06785494027924897</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3006,43 +3006,43 @@
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.02911695021559176</v>
+        <v>0.07424051053772911</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.06476323273079866</v>
+        <v>0.0002073483662680379</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.007170336572743037</v>
+        <v>-0.08448975050449033</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.01109948894706645</v>
+        <v>0.03485527996285789</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.05281467021775441</v>
+        <v>-0.05819654987608901</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.005080248793214366</v>
+        <v>-0.02514182370455493</v>
       </c>
       <c r="DJ5" t="n">
         <v>0</v>
@@ -3051,25 +3051,25 @@
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
         <v>0</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.01297927519932442</v>
+        <v>0.004733525995122724</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.02333052173569952</v>
+        <v>-0.02976716613869682</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.03276891655435538</v>
+        <v>0.01010434674055084</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
@@ -3078,25 +3078,25 @@
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.02569152807621262</v>
+        <v>-0.08613129613890008</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.04150942564668058</v>
+        <v>-0.103567904242373</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0484404037941368</v>
+        <v>0.01606984898167497</v>
       </c>
       <c r="EB5" t="n">
         <v>-0</v>
@@ -3105,106 +3105,106 @@
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.06071616520240144</v>
+        <v>0.04220727171019389</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.07666698843186333</v>
+        <v>-0.008871129078370378</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.02216706128075691</v>
+        <v>-0.1081337302130083</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.05712332408313821</v>
+        <v>-0.02642473099483145</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.03881060657381327</v>
+        <v>-0.06230559533155983</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.03223641754946454</v>
+        <v>-0.06947591603911558</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
         <v>0</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.03253306991344104</v>
+        <v>0.07162016775386094</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.064556199201022</v>
+        <v>0.002425315165800114</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.0013820549990888</v>
+        <v>-0.1032291851272208</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.03605137920614448</v>
+        <v>0.08856424182334126</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.02655214527233019</v>
+        <v>0.01578178791372964</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02007041507036819</v>
+        <v>-0.09628925843565705</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
@@ -3213,52 +3213,52 @@
         <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.01215350881855177</v>
+        <v>0.006500375738531301</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.005453337755829622</v>
+        <v>-0.009784902325203196</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001368967525424525</v>
+        <v>0.03694452572031228</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.02588997941357694</v>
+        <v>0.08735663781011467</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.005649284995072159</v>
+        <v>-0.09323427629476745</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3847,19 +3847,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.08277209790187949</v>
+        <v>0.1102182048284811</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06716382879388055</v>
+        <v>-0.01868792974120921</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02707531137749772</v>
+        <v>-0.03383518972897074</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3871,28 +3871,28 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04379225053928926</v>
+        <v>0.1171695167845668</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05043185674399209</v>
+        <v>-0.04489945984521498</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0188603932171013</v>
+        <v>-0.0207684962902985</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0134002604294596</v>
+        <v>0.07231620552176085</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.003738666059521553</v>
+        <v>-0.02902400648288334</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02505694036391492</v>
+        <v>0.03903888227005217</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>-0</v>
@@ -3928,34 +3928,34 @@
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.007846573499027351</v>
+        <v>0.01186305341893919</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01380494437432653</v>
+        <v>0.01957490270963385</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.01375534323632986</v>
+        <v>-0.03992354250379355</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04493940615869069</v>
+        <v>0.02882030209592831</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,43 +3964,43 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.004282063988440749</v>
+        <v>-0.03366408312215305</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.002029677656482399</v>
+        <v>-0.04993068287294935</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1231805654202604</v>
+        <v>0.3118729293152105</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.07186048141952171</v>
+        <v>-0.1406085359335357</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.03478699054066588</v>
+        <v>-0.1428479661312316</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,79 +4009,79 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03571787498888655</v>
+        <v>-0.05803009802483158</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.05556289847363112</v>
+        <v>-0.02204691027404696</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.01675111708578665</v>
+        <v>0.003008767857171972</v>
       </c>
       <c r="BI7" t="n">
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.042145747297763</v>
+        <v>0.1003918958282956</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0112863009549393</v>
+        <v>0.1087481240167207</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01372832059882201</v>
+        <v>0.09053000644786889</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05971245248352192</v>
+        <v>0.2030622613752462</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.03186659699892978</v>
+        <v>-0.06081225521542644</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.001922442768370668</v>
+        <v>-0.01511673057520972</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
@@ -4090,25 +4090,25 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02035972093833701</v>
+        <v>-0.05286722018616807</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01671746303391823</v>
+        <v>0.02727810270178341</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01969179427136114</v>
+        <v>0.02370845371242012</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
         <v>-0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.006449987165488326</v>
+        <v>-0.04006598073131451</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.004640930915138444</v>
+        <v>0.04603336664647709</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.004026236237181653</v>
+        <v>-0.003018507084927124</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,25 +4138,25 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01007095200631755</v>
+        <v>-0.05049919285773449</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01684022329428997</v>
+        <v>0.0151146570474752</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.02650864645398143</v>
+        <v>0.03135504086933209</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4171,52 +4171,52 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01365856477851009</v>
+        <v>-0.04503706814599441</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04033244163628231</v>
+        <v>0.0199845269416251</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.006951731512641838</v>
+        <v>0.005162012010492946</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.01843032520186855</v>
+        <v>-0.0009891285062963247</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.02870951726445498</v>
+        <v>-0.04315065078113571</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.03178251905618415</v>
+        <v>-0.01014440863298684</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
         <v>-0</v>
@@ -4225,7 +4225,7 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01835782219204482</v>
+        <v>0.04248663900775184</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
@@ -4234,16 +4234,16 @@
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03826735725866521</v>
+        <v>-0.1216423805988189</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.02025599082337503</v>
+        <v>0.00878283889211302</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,25 +4252,25 @@
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.005064440767972325</v>
+        <v>0.0003183649904375157</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.003006559176001465</v>
+        <v>-0.03492462216740951</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01250659344195434</v>
+        <v>0.01484848061414474</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,25 +4279,25 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0172478238659368</v>
+        <v>-0.008598247190902667</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.009586099390762236</v>
+        <v>-0.09675040953956535</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.02287407173370488</v>
+        <v>0.04686717951083639</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
@@ -4306,25 +4306,25 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.004520143851073927</v>
+        <v>-0.06517649779914407</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
         <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01233887985807303</v>
+        <v>0.0106488609959957</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02731679161598729</v>
+        <v>0.01534031403643948</v>
       </c>
       <c r="FD7" t="n">
         <v>-0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
@@ -4333,19 +4333,19 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04389000073714311</v>
+        <v>-0.04502148920168818</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03937891821099124</v>
+        <v>0.07852892673641559</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.02551665017994227</v>
+        <v>-0.01697574836390966</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4357,37 +4357,37 @@
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.004715447351098126</v>
+        <v>0.01678815129552948</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.001361224181294795</v>
+        <v>-0.02279588763038741</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.03426172320746369</v>
+        <v>-0.08955401417283416</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01655471909209086</v>
+        <v>-0.05234862096236154</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.01314246139579254</v>
+        <v>0.03895899459892398</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,16 +4416,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.290425399178024</v>
+        <v>0.1820432779388726</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1151436153862259</v>
+        <v>-0.07990700554256332</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.004110251391793115</v>
+        <v>-0.01897405097733715</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1821972589989406</v>
+        <v>0.1658134154504345</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07957818776972328</v>
+        <v>-0.06408292678036526</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.05274217828019751</v>
+        <v>-0.02948442675824711</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4470,76 +4470,76 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1089951034721374</v>
+        <v>0.0598127677126267</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01879569361958783</v>
+        <v>-0.03773893325246182</v>
       </c>
       <c r="W8" t="n">
-        <v>0.08045209469403682</v>
+        <v>-0.03935074396336369</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.01369194631231472</v>
+        <v>0.001284213115814607</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.003695293370672599</v>
+        <v>0.0389930768742693</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0004986916895140214</v>
+        <v>0.01095541434550769</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.04301839198174229</v>
+        <v>0.1041907078337445</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.05197888495521381</v>
+        <v>-0.04561914815578827</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006539990571122194</v>
+        <v>0.06343335475821145</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,19 +4548,19 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4558897485956165</v>
+        <v>0.2546370812583763</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.004007819354586472</v>
+        <v>-0.09010584107570267</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.2006572038024017</v>
+        <v>-0.09326633559506139</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02221999925294738</v>
+        <v>-0.02233537775146438</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.0863369060470543</v>
+        <v>-0.03005786566372059</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1676048428307484</v>
+        <v>-0.03482841141511683</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4596,7 +4596,7 @@
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -4605,22 +4605,22 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02649577507722478</v>
+        <v>0.004113871761362401</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.1038829842968491</v>
+        <v>0.009921825853983298</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.05347963655349115</v>
+        <v>0.06137392213829093</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4632,49 +4632,49 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2641171095799836</v>
+        <v>0.1989401569728718</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.01900634561088884</v>
+        <v>-0.08095364393449821</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.06126849385272837</v>
+        <v>-0.04196653635546956</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
         <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1023330343960694</v>
+        <v>-0.09159607219704508</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.02985292713628019</v>
+        <v>0.07489570904515704</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.03335426881167574</v>
+        <v>-0.009387714934715971</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,52 +4686,52 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.02255551863832322</v>
+        <v>-0.02992848921852534</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.04163167851452002</v>
+        <v>0.05562883893560844</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.05064263702303881</v>
+        <v>0.01925785987338079</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.09177473313100271</v>
+        <v>-0.08897677181439774</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.04630983931516864</v>
+        <v>0.08177014176897263</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02545300105255937</v>
+        <v>0.001194563054324951</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,22 +4740,22 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.04775995363884483</v>
+        <v>-0.04627213972147454</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.008897158827666986</v>
+        <v>0.02882862092051947</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01741061146200306</v>
+        <v>-0.04388376389990053</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
@@ -4767,19 +4767,19 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.05974998230138617</v>
+        <v>-0.06085902066206113</v>
       </c>
       <c r="DP8" t="n">
         <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.01255572043867159</v>
+        <v>0.04548009435014423</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.06000098750786281</v>
+        <v>-0.01544811846220782</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4791,55 +4791,55 @@
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02865940384696249</v>
+        <v>0.06047853155131513</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.004791464988171639</v>
+        <v>-0.06277015790233208</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.0631640605234883</v>
+        <v>0.005361566055898867</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.0604535448513261</v>
+        <v>-0.04679755032745882</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.04751630855780068</v>
+        <v>0.04582948030170641</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.03167750400235547</v>
+        <v>-3.97982107990116e-05</v>
       </c>
       <c r="EK8" t="n">
         <v>-0</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
@@ -4848,22 +4848,22 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.1003145300011566</v>
+        <v>-0.03645980759469999</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.04317488347934209</v>
+        <v>0.04553994220358742</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.001463999931214064</v>
+        <v>-0.01836992872988916</v>
       </c>
       <c r="ET8" t="n">
         <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4872,25 +4872,25 @@
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.09806264359335309</v>
+        <v>-0.1062301785041175</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.04912495199463283</v>
+        <v>0.08184617937765286</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.03559777465874401</v>
+        <v>-0.01211864340848936</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
@@ -4902,70 +4902,70 @@
         <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.01002526433995624</v>
+        <v>-0.03587183289022857</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.07962627994422883</v>
+        <v>0.02972118377624881</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.08336900793803732</v>
+        <v>-0.01442734849675253</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.004795745233922251</v>
+        <v>0.0006900325541353</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0335917902920578</v>
+        <v>0.03388634986280975</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.009072047949348532</v>
+        <v>-0.009136389260001737</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.06156170590541146</v>
+        <v>-0.05858538135135227</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.04908907894877994</v>
+        <v>0.02029054854767551</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
         <v>-0</v>
@@ -4974,10 +4974,10 @@
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,19 +4985,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1963246049062023</v>
+        <v>0.4729639012579293</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03612964913872955</v>
+        <v>-0.08988273284050888</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08022428123333844</v>
+        <v>-0.04483851196322833</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -5012,25 +5012,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1198626792177589</v>
+        <v>0.5048934025188621</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02907046493140132</v>
+        <v>-0.1546358360856401</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0862744144123274</v>
+        <v>0.01988789132399562</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03002309954734986</v>
+        <v>0.1392197214104144</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,40 +5048,40 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0401935001320795</v>
+        <v>-0.04624583536628187</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01628238726287019</v>
+        <v>0.01872437496707133</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.857096086794906e-11</v>
+        <v>1.695753024989372e-11</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.00474093080783889</v>
+        <v>0.02538489024859001</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.0001871592630308599</v>
+        <v>0.001482425931885129</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5093,19 +5093,19 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.03977290449353167</v>
+        <v>0.1779483691682923</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.02369872565066485</v>
+        <v>0.0458914416238796</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.0493811752750669</v>
+        <v>-0.09085602809646573</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
@@ -5114,40 +5114,40 @@
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2172362154785204</v>
+        <v>0.7563152368538516</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.05846893837622037</v>
+        <v>-0.3416978804698966</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.1311568189656266</v>
+        <v>-0.1438599733266652</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0739518985112531</v>
+        <v>0.01182368388759849</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.07038029489911798</v>
+        <v>-0.1056667247385352</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.0341280821150924</v>
+        <v>-0.09697577775870804</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.08808859859742324</v>
+        <v>0.04409509847257986</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01860162181355178</v>
+        <v>0.1399700027193295</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01297540290526203</v>
+        <v>0.002207636071215538</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1003256815215423</v>
+        <v>0.558188352077609</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.03691311147088434</v>
+        <v>-0.1271066686261328</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.03662549471940964</v>
+        <v>-0.02332235291945009</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5222,52 +5222,52 @@
         <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.05277788879995807</v>
+        <v>-0.2442596350306672</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.008540032533169909</v>
+        <v>0.06177325692498706</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.04696574224620349</v>
+        <v>0.04567519623624947</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.004369681528110137</v>
+        <v>-0.2000553101816585</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01349371328022772</v>
+        <v>0.1185119812687814</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.02116303873884218</v>
+        <v>0.08424958594057025</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,31 +5276,31 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.04207367702618683</v>
+        <v>-0.2465078176355445</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.006740267536760791</v>
+        <v>0.01423414562359699</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.05126015493488341</v>
+        <v>0.04570842642521504</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.02028137269876402</v>
+        <v>-0.05423056810554649</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
@@ -5318,43 +5318,43 @@
         <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02721976033505227</v>
+        <v>-0.1566238747856468</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.008991089018483559</v>
+        <v>0.0886784394347309</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.0008068609718749328</v>
+        <v>-0.08551190338128588</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.03256321966933694</v>
+        <v>0.03121008638614471</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.002330476039074274</v>
+        <v>-0.1197631698159788</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.02306603753041918</v>
+        <v>0.09979216940028837</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,13 +5372,13 @@
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03339235491931581</v>
+        <v>-0.0796634900576623</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.02275571976439963</v>
+        <v>-0.1730955077730459</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
@@ -5390,46 +5390,46 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.03321991154388639</v>
+        <v>-0.04860584668637648</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.009961895041841511</v>
+        <v>-0.05779722865940638</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.04023310416937334</v>
+        <v>0.01388463016133661</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.03507320674971073</v>
+        <v>-0.1076393889997294</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.03831951403276122</v>
+        <v>-0.2019831999880533</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.04931610069551155</v>
+        <v>0.1457104719597088</v>
       </c>
       <c r="EU9" t="n">
         <v>-0</v>
@@ -5444,34 +5444,34 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.04130210195835396</v>
+        <v>-0.289248627291402</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.01012227138316581</v>
+        <v>0.01746503017869754</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.05334070821782295</v>
+        <v>0.04078373598023107</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01385074763217417</v>
+        <v>-0.2616460251824521</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,25 +5480,25 @@
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.0403500297518271</v>
+        <v>0.1586525646296216</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.02746926079259025</v>
+        <v>-0.01021273440217385</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0005095744947192064</v>
+        <v>0.007956825488361907</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
@@ -5507,10 +5507,10 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.00217790234920336</v>
+        <v>-0.01563200882255918</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.02652499228001978</v>
+        <v>-0.01503121402025093</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,13 +5522,13 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.007979189600616698</v>
+        <v>-0.05605843953243086</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.04096415071351164</v>
+        <v>-0.05635092108175524</v>
       </c>
       <c r="GE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.369452495385275</v>
+        <v>0.1941685536768584</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1013998995807664</v>
+        <v>-0.08556566278213566</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.06573226294616591</v>
+        <v>-0.01347419893938582</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2120957177965082</v>
+        <v>0.1782242032570245</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07356719001551794</v>
+        <v>-0.0786203537147165</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06544750744951768</v>
+        <v>-0.0325719191832963</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5608,70 +5608,70 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1204905895563734</v>
+        <v>0.05306612148026063</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.02595351875241237</v>
+        <v>-0.03033852961501285</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03537225613873445</v>
+        <v>-0.03984312902584323</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.007460716756691931</v>
+        <v>-0.006830819497961021</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0008489301831563534</v>
+        <v>0.01070509767024515</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.020096278949777e-14</v>
+        <v>-1.796210823380183e-11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.05830222755393322</v>
+        <v>0.07556706624277869</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.04713410437117187</v>
+        <v>-0.01464796351958333</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.04482480328418563</v>
+        <v>0.06580668986484098</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,25 +5680,25 @@
         <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4559076200495461</v>
+        <v>0.2457507885609617</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.01572780124855175</v>
+        <v>-0.04395529473783957</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.07157070958630475</v>
+        <v>-0.08036112219570626</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,25 +5707,25 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01563332822343334</v>
+        <v>-0.02358953723089356</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.08030690333432859</v>
+        <v>-0.04855939256758733</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1581471774590274</v>
+        <v>-0.04924350683318695</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,31 +5734,31 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05411218338191424</v>
+        <v>-0.00787210821501229</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0687848412262671</v>
+        <v>0.0133727151233248</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1007151398061091</v>
+        <v>0.04167994827675408</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,46 +5767,46 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2421395074013136</v>
+        <v>0.1790653731881285</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01112554473279912</v>
+        <v>-0.0535179153775428</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.02738620094898092</v>
+        <v>-0.02859251229927609</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.109900793654345</v>
+        <v>-0.08693987664838597</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.009490052186799644</v>
+        <v>0.05698830057238696</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01627999904936385</v>
+        <v>-0.004328749844833838</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5818,25 +5818,25 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001774329158069062</v>
+        <v>-0.02841012469249852</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.04703598695042903</v>
+        <v>0.04703535370441199</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05837665402184962</v>
+        <v>0.02770672576097233</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5845,22 +5845,22 @@
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.09978636303152627</v>
+        <v>-0.08695815060250126</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03096441463827811</v>
+        <v>0.05909227574858425</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.02460056662900829</v>
+        <v>0.0007169536610873479</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5878,19 +5878,19 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.04376537211676935</v>
+        <v>-0.04918397383565717</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.02007857579041893</v>
+        <v>0.01214251275696449</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05854944295177829</v>
+        <v>-0.06397996921417906</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
@@ -5902,22 +5902,22 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.04795114214704271</v>
+        <v>-0.0436611358632459</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.04267795234537584</v>
+        <v>-0.01154241153850249</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.06823054785972649</v>
+        <v>-0.02509555646027128</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5929,55 +5929,55 @@
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.05121958622435177</v>
+        <v>0.06799526339864272</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.005076981750471363</v>
+        <v>0.02597196655721506</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.08286297323497747</v>
+        <v>-0.01043428600914397</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.07793495638143105</v>
+        <v>-0.06109570134785747</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.03486930015594186</v>
+        <v>0.04400441653392284</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03398630538260509</v>
+        <v>0.01181030927585122</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
@@ -5986,22 +5986,22 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.06290502150818866</v>
+        <v>-0.01853063139563465</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.02285271700290034</v>
+        <v>0.04111755682799255</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.01963136340197826</v>
+        <v>-0.04064388045024719</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6013,16 +6013,16 @@
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.09840502068736345</v>
+        <v>-0.1000565640498717</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.02144475551351209</v>
+        <v>0.06991967333670218</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01343004264223757</v>
+        <v>-0.01404148890015672</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6034,88 +6034,88 @@
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.02484313499137715</v>
+        <v>-0.04915699171368731</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.05832459046954028</v>
+        <v>0.05658742678869412</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03845832198015069</v>
+        <v>0.0001843707210086795</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.000298292063296477</v>
+        <v>0.0007497883737325234</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.03786377768479482</v>
+        <v>0.08938269475806138</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.001299148366373883</v>
+        <v>-0.003013617497271018</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.006454464405265211</v>
+        <v>-0.05682073988926754</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.05388912409241445</v>
+        <v>0.01886708333041794</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6668356609245875</v>
+        <v>0.4247667929123793</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09138093644072058</v>
+        <v>0.1683036702528294</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5202297718684074</v>
+        <v>-0.2031421215158815</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,25 +6150,25 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4454240075589211</v>
+        <v>0.4870957756061594</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.002467693476538583</v>
+        <v>0.1325302652103379</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4795527449898611</v>
+        <v>-0.1364946012621575</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09207031619208046</v>
+        <v>0.1643837335339415</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1260521697527246</v>
+        <v>-0.1775564412688443</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.02636512947258844</v>
+        <v>0.03360703526062258</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
@@ -6204,34 +6204,34 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02058873257815178</v>
+        <v>0.007285429321961598</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.001433126022435056</v>
+        <v>-0.04525242101995145</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.003064009853591515</v>
+        <v>-0.03405722241147301</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1393708738589745</v>
+        <v>0.1333297891575781</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,52 +6240,52 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.08105578715078299</v>
+        <v>-0.003158291085417886</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.1446867465134154</v>
+        <v>-0.3590756153851545</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.6607335768442675</v>
+        <v>1.007313525406068</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.1826839631404707</v>
+        <v>0.0615934118313734</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.5715835598001668</v>
+        <v>-0.2867018287475057</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.2323744175641886</v>
+        <v>-0.1757010316259254</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,16 +6294,16 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1115648803942506</v>
+        <v>-0.260152016868625</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.1349616904216434</v>
+        <v>-0.2317991635410235</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,52 +6312,52 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1775732754742412</v>
+        <v>0.2190701789737671</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.003016045631010648</v>
+        <v>0.2807917242315589</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0.01901923442172123</v>
+        <v>-0.01119482343218669</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.353088232507915</v>
+        <v>0.5656664514868395</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.1224179752869315</v>
+        <v>-0.01473221079929116</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.3523598386990945</v>
+        <v>-0.1972226397817942</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
@@ -6366,49 +6366,49 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1476918008076759</v>
+        <v>-0.2086406804257785</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.04528330497594123</v>
+        <v>0.02613170073742179</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.1539989850696778</v>
+        <v>0.06792134542394529</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.00264224402592006</v>
+        <v>-0.2268671577561253</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01516041643590084</v>
+        <v>0.1336114154891055</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.001922790816207683</v>
+        <v>0.1575806286763135</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,22 +6417,22 @@
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.131012510265307</v>
+        <v>-0.2033160124251094</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.02932748072161919</v>
+        <v>-0.0701751576065876</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.1708048902908345</v>
+        <v>0.04669163939533244</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
@@ -6441,82 +6441,82 @@
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01036071705035199</v>
+        <v>-0.07547002829577967</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0902621110449188</v>
+        <v>-0.1106339998250453</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0.06727806534180919</v>
+        <v>0.1776164895947905</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01629231846506594</v>
+        <v>0.01509977015200776</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.06165216420197732</v>
+        <v>-0.1517618996719274</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.02186380082498744</v>
+        <v>0.04764776779942391</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.01167189034064959</v>
+        <v>0.1181821586921906</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.002529823810793779</v>
+        <v>-0.2034171128718588</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.112786287316341</v>
+        <v>-0.03534126955104538</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
@@ -6525,64 +6525,64 @@
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.1240026364430513</v>
+        <v>-0.06089097971017159</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.04218177816190873</v>
+        <v>-0.1638038738140501</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.2012320785162084</v>
+        <v>-0.116793526761415</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.03512778565234963</v>
+        <v>-0.05430618144357531</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.02754428185507402</v>
+        <v>-0.1815644908576685</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.1169766412259322</v>
+        <v>0.2042129498830679</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.107365039028023</v>
+        <v>-0.2393850446828365</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
@@ -6591,52 +6591,52 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.03327410874900099</v>
+        <v>-0.07871020229463133</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.135459392428405</v>
+        <v>0.05953616036569982</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.1340763609143444</v>
+        <v>-0.2527169573734928</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0006551578433614827</v>
+        <v>0.1312926611891048</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0.05304880537662316</v>
+        <v>-0.1102083261356622</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03455290987305239</v>
+        <v>-0.04680235139380081</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,10 +6645,10 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0005881590457319924</v>
+        <v>0.0008835139592854208</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.1024236521458989</v>
+        <v>0.06830203837051659</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
@@ -6660,22 +6660,22 @@
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.06461164058843534</v>
+        <v>-0.1142047301323081</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.04337507152965339</v>
+        <v>-0.08749535780946802</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,27 +6684,27 @@
         <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.08571596852814577</v>
+        <v>-0.2416855540682909</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6577870721086606</v>
+        <v>0.3601239868547064</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06488255354255731</v>
+        <v>-0.0294698325654269</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1592061648844423</v>
+        <v>-0.204943926477184</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4946246808953869</v>
+        <v>0.4628329266000984</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.11099370191355</v>
+        <v>-0.004493488166245215</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -6743,19 +6743,19 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09088762545501745</v>
+        <v>0.06455662804438096</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2670154624651014</v>
+        <v>0.03147584475704118</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.01661090059498643</v>
+        <v>-0.3104961029730529</v>
       </c>
       <c r="X12" t="n">
         <v>-0</v>
@@ -6764,70 +6764,70 @@
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.020550770739138</v>
+        <v>0.01486033255907952</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05322599392047275</v>
+        <v>0.03426368201771803</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.008399337409260989</v>
+        <v>-0.1102427805751124</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.1641749471913008</v>
+        <v>-0.02346984405995797</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1755108658316181</v>
+        <v>0.160419988033258</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03822067318484414</v>
+        <v>-0.2990182319755694</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.087619807093307</v>
+        <v>-0.1976985520235192</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.7413946390180599</v>
+        <v>0.3739908861740799</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,25 +6836,25 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.3017490121802902</v>
+        <v>-0.312229549004192</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.02619935653202603</v>
+        <v>0.07030869686757311</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.04393619601999057</v>
+        <v>0.2147368368950226</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.2492225711004545</v>
+        <v>0.176785257311569</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.07854491394536492</v>
+        <v>-0.06638683785741981</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1133396724358727</v>
+        <v>0.1529295020316851</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,7 +6890,7 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.2172034320909325</v>
+        <v>0.3733744004042523</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6905,19 +6905,19 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.08244449564363467</v>
+        <v>-0.05608121461606204</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.4937745061341277</v>
+        <v>0.2074614544368789</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.1147148861675715</v>
+        <v>-0.1878524073592041</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -6926,79 +6926,79 @@
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.01034993774761286</v>
+        <v>0.1292787676702048</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1451355589683338</v>
+        <v>-0.1072838607047242</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01376585917897043</v>
+        <v>0.03451004054280821</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
       </c>
       <c r="CK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL12" t="n">
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>-0.1424061398109976</v>
+        <v>-0.002324680326567115</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03966374613120462</v>
+        <v>-0.1533806796353861</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1972453995756325</v>
+        <v>-0.01940277788678815</v>
       </c>
       <c r="CR12" t="n">
         <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.006044581257826189</v>
+        <v>0.1146119251236682</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1630054836483972</v>
+        <v>-0.1062943655990887</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01934900303858192</v>
+        <v>0.005035476724358831</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7013,19 +7013,19 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0.08162479399464474</v>
+        <v>0.07362370377822738</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.2972100996521185</v>
+        <v>0.004667852916580438</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07229653371361817</v>
+        <v>-0.103782407423144</v>
       </c>
       <c r="DJ12" t="n">
         <v>0</v>
@@ -7037,49 +7037,49 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0.02824586524991233</v>
+        <v>0.07512822453960087</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06187585985348974</v>
+        <v>-0.214767826953472</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.02691435019489701</v>
+        <v>-0.04585748916640977</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0.0001889283661507004</v>
+        <v>-0.08881257028855755</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.3369852033933889</v>
+        <v>-0.2760064323169923</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.2018081428717316</v>
+        <v>-0.1744051201675981</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7094,19 +7094,19 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0.05231051498740621</v>
+        <v>0.107439283591794</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.01577276569031298</v>
+        <v>0.04411793106237131</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.009731232638558065</v>
+        <v>-0.06430471639643998</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
@@ -7121,19 +7121,19 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01642946028795712</v>
+        <v>0.07505425393289794</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.0816131067808368</v>
+        <v>0.001687591578302009</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.2103457361077035</v>
+        <v>0.01115550967572982</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
@@ -7142,25 +7142,25 @@
         <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.009031905790030503</v>
+        <v>0.1369801439855398</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1588699082304847</v>
+        <v>-0.1398365067238001</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.05998212240565475</v>
+        <v>-0.004090693865395422</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7172,28 +7172,28 @@
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.02770695790180559</v>
+        <v>-0.0193733630213347</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.08744130300231727</v>
+        <v>-0.1616526689118759</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.06065565485073312</v>
+        <v>-0.07334894549510437</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7202,19 +7202,19 @@
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.000791130739672393</v>
+        <v>0.00183479298178219</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.07803066625414007</v>
+        <v>0.04293817742339484</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.04530830949380709</v>
+        <v>0.04840564678600705</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
@@ -7226,16 +7226,16 @@
         <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0.1454352681035027</v>
+        <v>0.001914138337135921</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.08397434774036848</v>
+        <v>-0.005472622928075941</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1418953507655331</v>
+        <v>0.251455703790521</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.04752250046186948</v>
+        <v>0.0367508927049181</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07197081270385532</v>
+        <v>-0.1568997837711279</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7285,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1066745863776339</v>
+        <v>0.2898443661650492</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.02061517385022311</v>
+        <v>-0.05639606391221885</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.04953149374328249</v>
+        <v>-0.1392135618343821</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,49 +7315,49 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02066703354063695</v>
+        <v>0.09124273630869585</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01184230150493463</v>
+        <v>-0.04950526283931772</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.002418968016409235</v>
+        <v>-0.004892061752361222</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.001473450765344417</v>
+        <v>-0.02102993125301586</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.006238307432118203</v>
+        <v>-0.05105970408984609</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.003258942822008387</v>
+        <v>0.008925649067200312</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
@@ -7369,34 +7369,34 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.02187779616075108</v>
+        <v>0.09377708685222642</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.005472131048793372</v>
+        <v>-0.02467130084164545</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.03891805891321568</v>
+        <v>-0.07355027329568951</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1122253208198411</v>
+        <v>0.55558114385338</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,25 +7405,25 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03522277902375249</v>
+        <v>-0.1763101671433369</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.09435434977615337</v>
+        <v>-0.2564264713790119</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03628516996742746</v>
+        <v>-0.1464035669353067</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,70 +7432,70 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03781551879173254</v>
+        <v>-0.02124543100226865</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.02041088288158266</v>
+        <v>-0.07872483618500141</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02429078433775001</v>
+        <v>0.1335380046985778</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.001838200394335454</v>
+        <v>0.09860867110934195</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.005952915126473582</v>
+        <v>0.05403587386536606</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.05902919083973723</v>
+        <v>0.2976700507317501</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02469036892128309</v>
+        <v>-0.0471346615889762</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.0275426896538986</v>
+        <v>-0.09889486178633605</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,34 +7504,34 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.03176284734325026</v>
+        <v>-0.1115047027804643</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001731734446727498</v>
+        <v>0.01904304278519724</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02496082789513697</v>
+        <v>0.05787408093103747</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.005457140659829258</v>
+        <v>-0.1136816425405872</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
@@ -7540,37 +7540,37 @@
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>9.666466228104374e-05</v>
+        <v>0.07200078419122752</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01883583075895193</v>
+        <v>0.0257914902410118</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.02853489399449124</v>
+        <v>-0.103464832394107</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.00362205815454712</v>
+        <v>-0.002005073445649848</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03031406045738811</v>
+        <v>0.08631563387743048</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7579,40 +7579,40 @@
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.02044677222340279</v>
+        <v>-0.1217216551130976</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.03922396120733526</v>
+        <v>-0.1414865267459436</v>
       </c>
       <c r="DJ13" t="n">
-        <v>4.65235126604855e-05</v>
+        <v>0.05234661215198388</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.008292544581153605</v>
+        <v>-0.06035996237161976</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
@@ -7621,16 +7621,16 @@
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01478814859460298</v>
+        <v>0.0008079847354668221</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002483731533719865</v>
+        <v>0.09274696938201919</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,46 +7639,46 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01977855194766084</v>
+        <v>-0.1022463490591942</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.00353643098367928</v>
+        <v>0.04655218247057236</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.009533677469311453</v>
+        <v>0.04497626263375212</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03259464076359346</v>
+        <v>-0.0270761523270793</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01384856406069506</v>
+        <v>-0.02913452715785731</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.03458994911213214</v>
+        <v>-0.0336706449680696</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7693,25 +7693,25 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01760771716943064</v>
+        <v>-0.01113887130529907</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.001477996618714651</v>
+        <v>-0.07431967892386927</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01215607117123011</v>
+        <v>-0.02964895387881553</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
@@ -7720,46 +7720,46 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0266551981913845</v>
+        <v>-0.1360623822727336</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.004037524655955336</v>
+        <v>-0.01045993277234261</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02646215716020259</v>
+        <v>0.0617842220351798</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0018384688502564</v>
+        <v>0.1051543965653032</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.006885761254684857</v>
+        <v>-0.01356127214748418</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.03387098457266617</v>
+        <v>0.09988371249183271</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.003132593208881262</v>
+        <v>-0.02983292628620553</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,43 +7783,43 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01216418452715884</v>
+        <v>0.04811074056957827</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01792650977571126</v>
+        <v>-0.08814659331551576</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.007391249136609368</v>
+        <v>-0.02435120264894068</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01858043641522469</v>
+        <v>0.09858930519231823</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.09218348329117208</v>
+        <v>0.148153821351277</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,40 +7839,40 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.07712476970384391</v>
+        <v>-0.007256845478434015</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0158063782918583</v>
+        <v>-0.05463911901243799</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05734426186088013</v>
+        <v>0.1618917465688139</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.05401019898709075</v>
+        <v>-0.05128653340460261</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0118441510516769</v>
+        <v>-0.05169871676335433</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01801727364977982</v>
+        <v>0.05264733406336815</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7893,37 +7893,37 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.008473901257902235</v>
+        <v>-0.04466446690676486</v>
       </c>
       <c r="X14" t="n">
-        <v>0.008297895238559705</v>
+        <v>0.004610042489536548</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.003718091537120181</v>
+        <v>-0.02073108627818696</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.002526350527515117</v>
+        <v>-0.05991137494878866</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.00317072937713271</v>
+        <v>0.001247714918613149</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7935,37 +7935,37 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01427015331961009</v>
+        <v>0.02153237977787304</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01333625421654921</v>
+        <v>-0.03100632390023144</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.01552366887124952</v>
+        <v>-0.0003521344080100226</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.08702892476159725</v>
+        <v>0.1907521604330564</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
@@ -7974,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.04855548358950695</v>
+        <v>-0.09730691176189148</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.01424976630622538</v>
+        <v>-0.08226697167021792</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7986,13 +7986,13 @@
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0165117046464522</v>
+        <v>-0.01223595151693418</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,13 +8001,13 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.04899267043793639</v>
+        <v>-0.01694248485320244</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.007805528117033524</v>
+        <v>-0.03439697668162712</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
         <v>-0</v>
@@ -8016,49 +8016,49 @@
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.02513773424376442</v>
+        <v>0.02478117507571168</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.01722452677685251</v>
+        <v>0.05459822860180513</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01807135109681814</v>
+        <v>0.01948160179390742</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.04762411284030008</v>
+        <v>0.1202305539727423</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.02791722110111156</v>
+        <v>-0.0217971366614466</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.002727754092677541</v>
+        <v>-0.03001956477175613</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,40 +8067,40 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.01768847279916633</v>
+        <v>-0.04342436287214076</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.01440280862740248</v>
+        <v>0.00660258088345334</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.007457868024042181</v>
+        <v>0.03800367331448282</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0008727398944646736</v>
+        <v>-0.03068766741966936</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,37 +8109,37 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.001577295683943146</v>
+        <v>0.03902976546696456</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.007745663253518544</v>
+        <v>0.02605615395011412</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.01253136926249428</v>
+        <v>-0.044229297973569</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.01342154891645108</v>
+        <v>0.001861356854775011</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.013403003516391</v>
+        <v>0.05118175641055083</v>
       </c>
       <c r="DB14" t="n">
         <v>-0</v>
@@ -8151,22 +8151,22 @@
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.01615331403762248</v>
+        <v>-0.04305074964559515</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01996407665070883</v>
+        <v>-0.06198690416275288</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.002783128322399203</v>
+        <v>0.01473817532232034</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,40 +8175,40 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.004695246089199174</v>
+        <v>0.006802028861512095</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.02372377748504089</v>
+        <v>-0.02712166943656099</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.01038355916969447</v>
+        <v>7.130441686000147e-05</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.01875197588805524</v>
+        <v>-0.007169019769029984</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
@@ -8217,64 +8217,64 @@
         <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01891293773375453</v>
+        <v>-0.02440276829886404</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.0004943652598487936</v>
+        <v>0.03161379248096082</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.01937975516341556</v>
+        <v>-0.02121044399784956</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.01254179986524919</v>
+        <v>-0.001205959922341941</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.009999124572950205</v>
+        <v>0.005440610572940496</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.00339399864236705</v>
+        <v>-0.02228044562415772</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.006710475934501059</v>
+        <v>0.008372253389815534</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0.00498627702058578</v>
+        <v>0.05586732524194063</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8283,25 +8283,25 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.01097041137339341</v>
+        <v>-0.04887794891393448</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01346541411067968</v>
+        <v>-0.008004511473938224</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.01312279032613648</v>
+        <v>0.03438666597222071</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.003118542633175628</v>
+        <v>0.06765946753166521</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
@@ -8325,25 +8325,25 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01527183391095824</v>
+        <v>-0.02000562048051363</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01032742288057255</v>
+        <v>0.04852662429457946</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.002609952653572577</v>
+        <v>-0.0129294351464874</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,43 +8352,43 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.007461402599146656</v>
+        <v>0.01482407040826325</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.008880038534491128</v>
+        <v>-0.06408057649287782</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.004517011376843525</v>
+        <v>-0.03258221599975918</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.004559554677983711</v>
+        <v>0.04053065999521642</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
         <v>0</v>
@@ -8396,49 +8396,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3825054381972509</v>
+        <v>0.2403902927783496</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1295718280281895</v>
+        <v>-0.1448395679685561</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.03554603741119905</v>
+        <v>-0.04947163745183296</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2692596159585908</v>
+        <v>0.2476777091947362</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1443650703601926</v>
+        <v>-0.1938942821283707</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05507033013629802</v>
+        <v>-0.08556227119605928</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -8447,139 +8447,139 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0979334886559094</v>
+        <v>0.04263523707820831</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.009199408700951959</v>
+        <v>-0.03268625539837111</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1002845668535296</v>
+        <v>-0.01271176583509151</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1097212600723173</v>
+        <v>-0.006785116965245148</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.01275316227231089</v>
+        <v>-0.03624939968708601</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.004684062040889664</v>
+        <v>-0.02659475573101067</v>
       </c>
       <c r="AG15" t="n">
         <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.01718640562800808</v>
+        <v>0.0513190687710371</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.08039938236282655</v>
+        <v>-0.02894970616418884</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.09378628563186946</v>
+        <v>0.03680276943466498</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.3470235833320461</v>
+        <v>0.2066352960900407</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.0705290141502008</v>
+        <v>-0.1432090137638284</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1510945354828138</v>
+        <v>-0.1388758040064075</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0280218641776072</v>
+        <v>-0.005121701721274469</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.0525785828105176</v>
+        <v>-0.04515340639292391</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1151895479511728</v>
+        <v>-0.008346158216085064</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,19 +8588,19 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.05610611207400458</v>
+        <v>0.0014461024743723</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.062022706213572</v>
+        <v>0.06683134147096108</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.2108666641152866</v>
+        <v>0.04432256651531875</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
         <v>0</v>
@@ -8609,22 +8609,22 @@
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1652574332661421</v>
+        <v>0.1615575385851751</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.02477503610593524</v>
+        <v>-0.1041775051442233</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.108158712621496</v>
+        <v>-0.0197855151420645</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -8633,106 +8633,106 @@
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.09412784263232189</v>
+        <v>-0.06958658030645293</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02496945890204952</v>
+        <v>0.09077651299239364</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.01279369602290429</v>
+        <v>0.01063036620050162</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.02650006183309025</v>
+        <v>-0.04931080728937515</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.06529952338266762</v>
+        <v>0.1083800508258244</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1125742349341691</v>
+        <v>0.04051513840434908</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.08833512511385959</v>
+        <v>-0.08035870157293792</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.04472138101779075</v>
+        <v>0.1039167726819733</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.005585346013523271</v>
+        <v>0.01689408152994425</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.01304290170053532</v>
+        <v>-0.02595191415694129</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.002281814490035483</v>
+        <v>0.02065781932162561</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.008105809555932037</v>
+        <v>-0.04401548868579578</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
@@ -8747,19 +8747,19 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.007110480545563786</v>
+        <v>-0.03114349496371527</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.1876861804452315</v>
+        <v>0.02144981063963296</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.05124595377187918</v>
+        <v>0.00576650665018195</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8768,85 +8768,85 @@
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.06761467884679237</v>
+        <v>-0.02678699643614543</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.009802160706626661</v>
+        <v>0.03638138481489344</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.04042061658674052</v>
+        <v>-0.0531935358398629</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1123408669080374</v>
+        <v>-0.05411041064207078</v>
       </c>
       <c r="EH15" t="n">
         <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.08526195053075411</v>
+        <v>0.08466880179888354</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.08047397001822125</v>
+        <v>0.02674672446043411</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.09632858065458152</v>
+        <v>-0.03006480108136068</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.08593934296885913</v>
+        <v>0.05763206998229576</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.01677120098294135</v>
+        <v>-0.006533947060815256</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,43 +8858,43 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.08412554456487613</v>
+        <v>-0.09151122822008681</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.02883657746200557</v>
+        <v>0.1080443960668404</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.001256361317457984</v>
+        <v>0.0106587884889139</v>
       </c>
       <c r="FC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.03351346494242671</v>
+        <v>0.06444265004698418</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.08379011569382031</v>
+        <v>-0.09105420781394773</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.04158659051212851</v>
+        <v>-0.003556932327843597</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8906,22 +8906,22 @@
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01219258748204293</v>
+        <v>-0.02900547618441541</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.116488373385353</v>
+        <v>0.09605155863302116</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.00700136580491989</v>
+        <v>0.05083853755783783</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
@@ -8939,25 +8939,25 @@
         <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.01274747699636857</v>
+        <v>-0.03835696659480443</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.06602930240287191</v>
+        <v>0.05766406488747366</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2114232017943382</v>
+        <v>0.3620649324463009</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,13 +9546,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06196800011976527</v>
+        <v>0.1382971669425678</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1262091294642709</v>
+        <v>-0.3142805222848497</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
@@ -9561,79 +9561,79 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1741354513712348</v>
+        <v>0.5360379047515097</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.03452851553280471</v>
+        <v>0.1023230080620204</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1039640560666887</v>
+        <v>-0.2359346091164473</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02442292409608628</v>
+        <v>0.05241433252621328</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.01749334998965546</v>
+        <v>-0.1455008812626171</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.005189519451154903</v>
+        <v>-0.1015653654853333</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
         <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.002260419021689965</v>
+        <v>-0.06911333702631754</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01010492029047274</v>
+        <v>-0.2562393282879166</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0007316434694098053</v>
+        <v>-0.07263006763320126</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.03111085224127539</v>
+        <v>0.110285345700121</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -9654,10 +9654,10 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.004351194814931581</v>
+        <v>-0.02993796112906152</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.04200436837301656</v>
+        <v>-0.1538954842181542</v>
       </c>
       <c r="AQ17" t="n">
         <v>-0</v>
@@ -9669,10 +9669,10 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1468394188072978</v>
+        <v>0.7856848340335523</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,25 +9681,25 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.0192282377934743</v>
+        <v>-0.121646132575643</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.07870534433186403</v>
+        <v>-0.1075443177962125</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04487527959357566</v>
+        <v>-0.1901470979612716</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,52 +9708,52 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.05398514984617187</v>
+        <v>-0.06685740825794476</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.04666439540654739</v>
+        <v>-0.1769261497984881</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.03391884584701934</v>
+        <v>0.166957405576633</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>-0.001512571223926119</v>
+        <v>0.1047859429419036</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.02150741260265698</v>
+        <v>0.08996288837030197</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.07589824267524867</v>
+        <v>0.3431671598791073</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,91 +9762,91 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02317472099708712</v>
+        <v>-0.05801432301735288</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.04951338655626818</v>
+        <v>-0.2343737833074868</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.03876553896406714</v>
+        <v>-0.1231211673881066</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.002091944733646734</v>
+        <v>0.01045489397502972</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.03116492994115761</v>
+        <v>0.11162818045884</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0002410348301434478</v>
+        <v>-0.2409145071760173</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.006713783449440961</v>
+        <v>0.1468510745402667</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.0129795812891368</v>
+        <v>0.08838428565120827</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.03121891785665533</v>
+        <v>-0.1195678329631115</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.003847181005839808</v>
+        <v>-0.02099277309598156</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.03619167284156776</v>
+        <v>0.1335446519604371</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9855,58 +9855,58 @@
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01104531704698346</v>
+        <v>-0.02024509451355963</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03044872738243387</v>
+        <v>-0.1936549700474201</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.0006882768643684497</v>
+        <v>-0.02820215381437092</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.01231435569425358</v>
+        <v>-0.03712034900960896</v>
       </c>
       <c r="DP17" t="n">
         <v>0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0256834115657716</v>
+        <v>0.04037098606286241</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.001277898317020045</v>
+        <v>0.1627742869705175</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,19 +9915,19 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.02105542919747567</v>
+        <v>-0.04692267805252104</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.01088892288362845</v>
+        <v>-0.1366791904198894</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.02262656207797716</v>
+        <v>0.04440459649201514</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
@@ -9942,115 +9942,115 @@
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.03642613736091141</v>
+        <v>-0.032971326811533</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.008356749274628624</v>
+        <v>-0.05210411663296304</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.03320547868614315</v>
+        <v>-0.007471755698695081</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO17" t="n">
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.01037561434038905</v>
+        <v>-0.01510598804912787</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.01205964578167396</v>
+        <v>-0.05661605448347013</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.01495213980873787</v>
+        <v>0.02587212049438966</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.02862399676362613</v>
+        <v>-0.1420390991843637</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.003653695084099186</v>
+        <v>-0.06039444891943221</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.03289626198734217</v>
+        <v>0.1182037902310936</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.007505585314548798</v>
+        <v>0.1767392197113344</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0003559414794758109</v>
+        <v>-0.07571621303834684</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.02419413880789404</v>
+        <v>-0.1466540923540713</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.01100129986428807</v>
+        <v>-0.1658537941950107</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,43 +10059,43 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.005970475864770957</v>
+        <v>0.02852605498582696</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.04217567169446682</v>
+        <v>-0.07479844429837608</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0183213464679312</v>
+        <v>0.0368493233030747</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01702372188505108</v>
+        <v>0.05853155603773631</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
